--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 14:08</t>
+    <t xml:space="preserve">2026-08-07 06:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:34</t>
+    <t xml:space="preserve">2026-08-13 12:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 12:59</t>
+    <t xml:space="preserve">2026-08-19 13:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 13:28</t>
+    <t xml:space="preserve">2026-08-28 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:08</t>
+    <t xml:space="preserve">2026-09-01 11:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:35</t>
+    <t xml:space="preserve">2026-09-04 20:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:09</t>
+    <t xml:space="preserve">2026-09-06 16:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2022_los_lagos_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:41</t>
+    <t xml:space="preserve">2026-09-08 11:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
